--- a/web/public/server_setup_template.xlsx
+++ b/web/public/server_setup_template.xlsx
@@ -1,58 +1,453 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="手順書" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="表紙" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="改訂履歴" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="前提条件" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="手順書" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="切り戻し手順" state="visible" r:id="rId8"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="115">
+  <si>
+    <t>EC2サーバー構築手順書</t>
+  </si>
+  <si>
+    <t>ドキュメントID</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>バージョン</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>対象システム</t>
+  </si>
+  <si>
+    <t>EC2サーバー構築演習</t>
+  </si>
+  <si>
+    <t>対象サーバー</t>
+  </si>
+  <si>
+    <t>承認欄</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>日付</t>
+  </si>
+  <si>
+    <t>作成</t>
+  </si>
+  <si>
+    <t>確認</t>
+  </si>
+  <si>
+    <t>承認</t>
+  </si>
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>前提条件</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>作業環境</t>
+  </si>
+  <si>
+    <t>OS: Amazon Linux 2023</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>インスタンスタイプ: t2.micro以上</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>必要権限</t>
+  </si>
+  <si>
+    <t>SSH接続権限</t>
+  </si>
+  <si>
+    <t>秘密鍵を事前に取得</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>sudo権限</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>事前準備</t>
+  </si>
+  <si>
+    <t>EC2インスタンスが起動していること</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>セキュリティグループでSSH(22)、HTTP(80)が許可されていること</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>確認事項</t>
+  </si>
+  <si>
+    <t>対象サーバーのパブリックIPアドレス</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>SSH接続ユーザー名</t>
+  </si>
+  <si>
+    <t>通常は ec2-user</t>
+  </si>
+  <si>
+    <t>手順番号</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>対象</t>
+  </si>
+  <si>
+    <t>手順（コマンド＋確認項目）</t>
+  </si>
+  <si>
+    <t>担当</t>
+  </si>
+  <si>
+    <t>開始時間(予定)</t>
+  </si>
+  <si>
+    <t>完了時間(予定)</t>
+  </si>
+  <si>
+    <t>開始時間(実施)</t>
+  </si>
+  <si>
+    <t>完了時間(実施)</t>
+  </si>
+  <si>
+    <t>1. ログイン</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>サーバーログイン</t>
+  </si>
+  <si>
+    <t>web_server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 対象サーバにSSHログインする
+ssh ec2-user@【IPアドレス】
+【確認】ログインできること</t>
+  </si>
+  <si>
+    <t>2. Webサーバー構築</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>Apacheインストール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apacheをインストールする
+# sudo dnf install httpd -y
+【確認】Complete! と表示されること</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>Apache起動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apacheを起動する
+# sudo systemctl start httpd
+【確認】エラーが出ないこと</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>自動起動設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 自動起動を有効にする
+# sudo systemctl enable httpd
+【確認】Created symlink... と表示される</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>動作確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apacheの動作を確認する
+# curl http://localhost
+【確認】HTMLが表示されること</t>
+  </si>
+  <si>
+    <t>3. データベース構築</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>MySQLインストール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. MySQLをインストールする
+# sudo dnf install mysql-server -y
+【確認】Complete! と表示されること</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>MySQL起動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. MySQLを起動する
+# sudo systemctl start mysqld
+【確認】エラーが出ないこと</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 自動起動を有効にする
+# sudo systemctl enable mysqld
+【確認】Created symlink... と表示される</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>初期設定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. MySQL初期設定を実行する
+# sudo mysql_secure_installation
+【確認】All done! と表示されること</t>
+  </si>
+  <si>
+    <t>パスワードを設定</t>
+  </si>
+  <si>
+    <t>4. 最終確認</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>サービス状態確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 各サービスの状態を確認する
+# systemctl status httpd
+# systemctl status mysqld
+【確認】両方 active (running) であること</t>
+  </si>
+  <si>
+    <t>切り戻し手順</t>
+  </si>
+  <si>
+    <t>※作業に失敗した場合、以下の手順で元の状態に戻してください</t>
+  </si>
+  <si>
+    <t>手順</t>
+  </si>
+  <si>
+    <t>R-1</t>
+  </si>
+  <si>
+    <t>Apacheの停止</t>
+  </si>
+  <si>
+    <t># sudo systemctl stop httpd</t>
+  </si>
+  <si>
+    <t>R-2</t>
+  </si>
+  <si>
+    <t>Apache自動起動の無効化</t>
+  </si>
+  <si>
+    <t># sudo systemctl disable httpd</t>
+  </si>
+  <si>
+    <t>R-3</t>
+  </si>
+  <si>
+    <t>Apacheのアンインストール</t>
+  </si>
+  <si>
+    <t># sudo dnf remove httpd -y</t>
+  </si>
+  <si>
+    <t>必要に応じて</t>
+  </si>
+  <si>
+    <t>R-4</t>
+  </si>
+  <si>
+    <t>MySQLの停止</t>
+  </si>
+  <si>
+    <t># sudo systemctl stop mysqld</t>
+  </si>
+  <si>
+    <t>R-5</t>
+  </si>
+  <si>
+    <t>MySQL自動起動の無効化</t>
+  </si>
+  <si>
+    <t># sudo systemctl disable mysqld</t>
+  </si>
+  <si>
+    <t>R-6</t>
+  </si>
+  <si>
+    <t>MySQLのアンインストール</t>
+  </si>
+  <si>
+    <t># sudo dnf remove mysql-server -y</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CAF50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF44336"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +455,78 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,206 +851,951 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A4:K18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="45.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="11" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>手順番号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>カテゴリ</v>
-      </c>
-      <c r="C1" t="str">
-        <v>作業内容</v>
-      </c>
-      <c r="D1" t="str">
-        <v>コマンド</v>
-      </c>
-      <c r="E1" t="str">
-        <v>備考</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Webサーバー構築</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Apacheをインストールする</v>
-      </c>
-      <c r="D2" t="str">
-        <v>sudo dnf install httpd -y</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Webサーバー構築</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Apacheを起動する</v>
-      </c>
-      <c r="D3" t="str">
-        <v>sudo systemctl start httpd</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Webサーバー構築</v>
-      </c>
-      <c r="C4" t="str">
-        <v>自動起動を設定する</v>
-      </c>
-      <c r="D4" t="str">
-        <v>sudo systemctl enable httpd</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
+      <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>動作確認</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Apacheの動作確認</v>
-      </c>
-      <c r="D5" t="str">
-        <v>curl http://localhost</v>
-      </c>
-      <c r="E5" t="str">
-        <v>テストページが表示されることを確認</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>データベース構築</v>
-      </c>
-      <c r="C6" t="str">
-        <v>MySQLをインストールする</v>
-      </c>
-      <c r="D6" t="str">
-        <v>sudo dnf install mysql-server -y</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>データベース構築</v>
-      </c>
-      <c r="C7" t="str">
-        <v>MySQLを起動する</v>
-      </c>
-      <c r="D7" t="str">
-        <v>sudo systemctl start mysqld</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>データベース構築</v>
-      </c>
-      <c r="C8" t="str">
-        <v>自動起動を設定する</v>
-      </c>
-      <c r="D8" t="str">
-        <v>sudo systemctl enable mysqld</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
+      <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>データベース構築</v>
-      </c>
-      <c r="C9" t="str">
-        <v>初期設定を実施する</v>
-      </c>
-      <c r="D9" t="str">
-        <v>sudo mysql_secure_installation</v>
-      </c>
-      <c r="E9" t="str">
-        <v>パスワード設定などを行う</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" ht="90" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A14:K14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>